--- a/cet4/result/71_律政女神_正义女王的逆袭/71_律政女神_正义女王的逆袭_学习版.xlsx
+++ b/cet4/result/71_律政女神_正义女王的逆袭/71_律政女神_正义女王的逆袭_学习版.xlsx
@@ -397,983 +397,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D54"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>wall</v>
       </c>
       <c r="B2" t="str">
-        <v>wall</v>
+        <v>/wɔːl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>墙</v>
       </c>
-      <c r="D2" t="str">
-        <v>wall(墙)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>law</v>
       </c>
       <c r="B3" t="str">
-        <v>law</v>
+        <v>/lɔː/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>法律</v>
       </c>
-      <c r="D3" t="str">
-        <v>law(法律)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>main</v>
       </c>
       <c r="B4" t="str">
-        <v>main</v>
+        <v>/meɪn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>主要</v>
       </c>
-      <c r="D4" t="str">
-        <v>main(主要)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>hell</v>
       </c>
       <c r="B5" t="str">
-        <v>hell</v>
+        <v>/hel,ˈheləvə/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vi./int.</v>
+      </c>
+      <c r="D5" t="str">
         <v>地狱</v>
       </c>
-      <c r="D5" t="str">
-        <v>hell(地狱)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>influential</v>
       </c>
       <c r="B6" t="str">
-        <v>influential</v>
+        <v>/ˌɪnfluˈenʃl/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>有影响力的</v>
       </c>
-      <c r="D6" t="str">
-        <v>influential(有影响力的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>mere</v>
       </c>
       <c r="B7" t="str">
-        <v>mere</v>
+        <v>/mɪr/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>仅仅</v>
       </c>
-      <c r="D7" t="str">
-        <v>mere(仅仅)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>study</v>
       </c>
       <c r="B8" t="str">
-        <v>study</v>
+        <v>/ˈstʌdi/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>研究</v>
       </c>
-      <c r="D8" t="str">
-        <v>study(研究)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>relevant</v>
       </c>
       <c r="B9" t="str">
-        <v>relevant</v>
+        <v>/ˈreləvənt/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>相关</v>
       </c>
-      <c r="D9" t="str">
-        <v>relevant(相关)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>harbour</v>
       </c>
       <c r="B10" t="str">
-        <v>harbour</v>
+        <v>/ˈhɑːrbər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>港口</v>
       </c>
-      <c r="D10" t="str">
-        <v>harbour(港口)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>crowd</v>
       </c>
       <c r="B11" t="str">
-        <v>crowd</v>
+        <v>/kraʊd/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>人群</v>
       </c>
-      <c r="D11" t="str">
-        <v>crowd(人群)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>probably</v>
       </c>
       <c r="B12" t="str">
-        <v>probably</v>
+        <v>/ˈprɑːbəbli/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>可能</v>
       </c>
-      <c r="D12" t="str">
-        <v>probably(可能)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>scent</v>
       </c>
       <c r="B13" t="str">
-        <v>scent</v>
+        <v>/sent/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>气味</v>
       </c>
-      <c r="D13" t="str">
-        <v>scent(气味)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>extra</v>
       </c>
       <c r="B14" t="str">
-        <v>extra</v>
+        <v>/ˈekstrə/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>额外</v>
       </c>
-      <c r="D14" t="str">
-        <v>extra(额外)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>build</v>
       </c>
       <c r="B15" t="str">
-        <v>build</v>
+        <v>/bɪld/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>建立</v>
       </c>
-      <c r="D15" t="str">
-        <v>build(建立)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>however</v>
       </c>
       <c r="B16" t="str">
-        <v>however</v>
+        <v>/haʊˈevər/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>然而</v>
       </c>
-      <c r="D16" t="str">
-        <v>however(然而)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>authority</v>
       </c>
       <c r="B17" t="str">
-        <v>authority</v>
+        <v>/əˈθɔːrəti/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>权威</v>
       </c>
-      <c r="D17" t="str">
-        <v>authority(权威)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>course</v>
       </c>
       <c r="B18" t="str">
-        <v>course</v>
+        <v>/kɔːrs/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>过程</v>
       </c>
-      <c r="D18" t="str">
-        <v>course(过程)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>stress</v>
       </c>
       <c r="B19" t="str">
-        <v>stress</v>
+        <v>/stres/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>压力</v>
       </c>
-      <c r="D19" t="str">
-        <v>stress(压力)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>somehow</v>
       </c>
       <c r="B20" t="str">
-        <v>somehow</v>
+        <v>/ˈsʌmhaʊ/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D20" t="str">
         <v>以某种方法</v>
       </c>
-      <c r="D20" t="str">
-        <v>somehow(以某种方法)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>sympathetic</v>
       </c>
       <c r="B21" t="str">
-        <v>crowd</v>
+        <v>/ˌsɪmpəˈθetɪk/</v>
       </c>
       <c r="C21" t="str">
-        <v>人群</v>
+        <v>n./adj.</v>
       </c>
       <c r="D21" t="str">
-        <v>crowd(人群)📢</v>
+        <v>同情的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>decision</v>
       </c>
       <c r="B22" t="str">
-        <v>sympathetic</v>
+        <v>/dɪˈsɪʒn/</v>
       </c>
       <c r="C22" t="str">
-        <v>同情的</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>sympathetic(同情的)📢</v>
+        <v>决定</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>chill</v>
       </c>
       <c r="B23" t="str">
-        <v>decision</v>
+        <v>/tʃɪl/</v>
       </c>
       <c r="C23" t="str">
-        <v>决定</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>decision(决定)📢</v>
+        <v>寒冷</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>abuse</v>
       </c>
       <c r="B24" t="str">
-        <v>chill</v>
+        <v>/əˈbjuːs/</v>
       </c>
       <c r="C24" t="str">
-        <v>寒冷</v>
+        <v>n./vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>chill(寒冷)📢</v>
+        <v>虐待</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>despair</v>
       </c>
       <c r="B25" t="str">
-        <v>extra</v>
+        <v>/dɪˈsper/</v>
       </c>
       <c r="C25" t="str">
-        <v>额外</v>
+        <v>n./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>extra(额外)📢</v>
+        <v>绝望</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>venture</v>
       </c>
       <c r="B26" t="str">
-        <v>abuse</v>
+        <v>/ˈventʃər/</v>
       </c>
       <c r="C26" t="str">
-        <v>虐待</v>
+        <v>n./v.</v>
       </c>
       <c r="D26" t="str">
-        <v>abuse(虐待)📢</v>
+        <v>冒险</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>dictate</v>
       </c>
       <c r="B27" t="str">
-        <v>despair</v>
+        <v>/ˈdɪkteɪt/</v>
       </c>
       <c r="C27" t="str">
-        <v>绝望</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>despair(绝望)📢</v>
+        <v>命令</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>convenient</v>
       </c>
       <c r="B28" t="str">
-        <v>venture</v>
+        <v>/kənˈviːniənt/</v>
       </c>
       <c r="C28" t="str">
-        <v>冒险</v>
+        <v>adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>venture(冒险)📢</v>
+        <v>方便</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>disclose</v>
       </c>
       <c r="B29" t="str">
-        <v>dictate</v>
+        <v>/dɪsˈkloʊz/</v>
       </c>
       <c r="C29" t="str">
-        <v>命令</v>
+        <v>vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>dictate(命令)📢</v>
+        <v>揭露</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>operator</v>
       </c>
       <c r="B30" t="str">
-        <v>convenient</v>
+        <v>/ˈɑːpəreɪtər/</v>
       </c>
       <c r="C30" t="str">
-        <v>方便</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>convenient(方便)📢</v>
+        <v>操作员</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>worse</v>
       </c>
       <c r="B31" t="str">
-        <v>disclose</v>
+        <v>/wɜːrs/</v>
       </c>
       <c r="C31" t="str">
-        <v>揭露</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>disclose(揭露)📢</v>
+        <v>更糟</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>house</v>
       </c>
       <c r="B32" t="str">
-        <v>operator</v>
+        <v>/haʊs/</v>
       </c>
       <c r="C32" t="str">
-        <v>操作员</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>operator(操作员)📢</v>
+        <v>房子</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>else</v>
       </c>
       <c r="B33" t="str">
-        <v>worse</v>
+        <v>/els/</v>
       </c>
       <c r="C33" t="str">
-        <v>更糟</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D33" t="str">
-        <v>worse(更糟)📢</v>
+        <v>其他</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>precaution</v>
       </c>
       <c r="B34" t="str">
-        <v>house</v>
+        <v>/prɪˈkɔːʃn/</v>
       </c>
       <c r="C34" t="str">
-        <v>房子</v>
+        <v>n./vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>house(房子)📢</v>
+        <v>预防</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>protect</v>
       </c>
       <c r="B35" t="str">
-        <v>else</v>
+        <v>/prəˈtekt/</v>
       </c>
       <c r="C35" t="str">
-        <v>其他</v>
+        <v>vt.</v>
       </c>
       <c r="D35" t="str">
-        <v>else(其他)📢</v>
+        <v>保护</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>medicine</v>
       </c>
       <c r="B36" t="str">
-        <v>precaution</v>
+        <v>/ˈmedɪsn/</v>
       </c>
       <c r="C36" t="str">
-        <v>预防</v>
+        <v>n./vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>precaution(预防)📢</v>
+        <v>医学</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>vigorous</v>
       </c>
       <c r="B37" t="str">
-        <v>protect</v>
+        <v>/ˈvɪɡərəs/</v>
       </c>
       <c r="C37" t="str">
-        <v>保护</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>protect(保护)📢</v>
+        <v>有力的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>movement</v>
       </c>
       <c r="B38" t="str">
-        <v>medicine</v>
+        <v>/ˈmuːvmənt/</v>
       </c>
       <c r="C38" t="str">
-        <v>医学</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>medicine(医学)📢</v>
+        <v>运动</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>feasible</v>
       </c>
       <c r="B39" t="str">
-        <v>vigorous</v>
+        <v>/ˈfiːzəbl/</v>
       </c>
       <c r="C39" t="str">
-        <v>有力的</v>
+        <v>adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>vigorous(有力的)📢</v>
+        <v>可行的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>cabinet</v>
       </c>
       <c r="B40" t="str">
-        <v>build</v>
+        <v>/ˈkæbɪnət/</v>
       </c>
       <c r="C40" t="str">
-        <v>建立</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>build(建立)📢</v>
+        <v>内阁</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>splendid</v>
       </c>
       <c r="B41" t="str">
-        <v>sympathetic</v>
+        <v>/ˈsplendɪd/</v>
       </c>
       <c r="C41" t="str">
-        <v>同情的</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>sympathetic(同情的)📢</v>
+        <v>极好的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>consume</v>
       </c>
       <c r="B42" t="str">
-        <v>influential</v>
+        <v>/kənˈsuːm/</v>
       </c>
       <c r="C42" t="str">
-        <v>有影响力的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>influential(有影响力的)📢</v>
+        <v>消耗</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>courage</v>
       </c>
       <c r="B43" t="str">
-        <v>movement</v>
+        <v>/ˈkɜːrɪdʒ/</v>
       </c>
       <c r="C43" t="str">
-        <v>运动</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>movement(运动)📢</v>
+        <v>勇气</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>trim</v>
       </c>
       <c r="B44" t="str">
-        <v>feasible</v>
+        <v>/trɪm/</v>
       </c>
       <c r="C44" t="str">
-        <v>可行的</v>
+        <v>vt./adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>feasible(可行的)📢</v>
+        <v>整齐</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>soda</v>
       </c>
       <c r="B45" t="str">
-        <v>cabinet</v>
+        <v>/ˈsoʊdə/</v>
       </c>
       <c r="C45" t="str">
-        <v>内阁</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>cabinet(内阁)📢</v>
+        <v>苏打</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>I</v>
       </c>
       <c r="B46" t="str">
-        <v>splendid</v>
+        <v>/aɪ/</v>
       </c>
       <c r="C46" t="str">
-        <v>极好的</v>
+        <v>n./pron.</v>
       </c>
       <c r="D46" t="str">
-        <v>splendid(极好的)📢</v>
+        <v>我</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>skill</v>
       </c>
       <c r="B47" t="str">
-        <v>relevant</v>
+        <v>/skɪl/</v>
       </c>
       <c r="C47" t="str">
-        <v>相关</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>relevant(相关)📢</v>
+        <v>技能</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>excessive</v>
       </c>
       <c r="B48" t="str">
-        <v>influential</v>
+        <v>/ɪkˈsesɪv/</v>
       </c>
       <c r="C48" t="str">
-        <v>有影响力的</v>
+        <v>adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>influential(有影响力的)📢</v>
+        <v>过多</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>pill</v>
       </c>
       <c r="B49" t="str">
-        <v>consume</v>
+        <v>/pɪl/</v>
       </c>
       <c r="C49" t="str">
-        <v>消耗</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>consume(消耗)📢</v>
+        <v>药丸</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>bed</v>
       </c>
       <c r="B50" t="str">
-        <v>courage</v>
+        <v>/bed/</v>
       </c>
       <c r="C50" t="str">
-        <v>勇气</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>courage(勇气)📢</v>
+        <v>床</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>minimum</v>
       </c>
       <c r="B51" t="str">
-        <v>trim</v>
+        <v>/ˈmɪnɪməm/</v>
       </c>
       <c r="C51" t="str">
-        <v>整齐</v>
+        <v>n./adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>trim(整齐)📢</v>
+        <v>最小</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>flour</v>
       </c>
       <c r="B52" t="str">
-        <v>mere</v>
+        <v>/ˈflaʊər/</v>
       </c>
       <c r="C52" t="str">
-        <v>仅仅</v>
+        <v>n./vt.</v>
       </c>
       <c r="D52" t="str">
-        <v>mere(仅仅)📢</v>
+        <v>面粉</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>beer</v>
       </c>
       <c r="B53" t="str">
-        <v>relevant</v>
+        <v>/bɪr/</v>
       </c>
       <c r="C53" t="str">
-        <v>相关</v>
+        <v>n./vi.</v>
       </c>
       <c r="D53" t="str">
-        <v>relevant(相关)📢</v>
+        <v>啤酒</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>believe</v>
       </c>
       <c r="B54" t="str">
-        <v>crowd</v>
+        <v>/bɪˈliːv/</v>
       </c>
       <c r="C54" t="str">
-        <v>人群</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D54" t="str">
-        <v>crowd(人群)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>harbour</v>
-      </c>
-      <c r="C55" t="str">
-        <v>港口</v>
-      </c>
-      <c r="D55" t="str">
-        <v>harbour(港口)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>house</v>
-      </c>
-      <c r="C56" t="str">
-        <v>房子</v>
-      </c>
-      <c r="D56" t="str">
-        <v>house(房子)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>soda</v>
-      </c>
-      <c r="C57" t="str">
-        <v>苏打</v>
-      </c>
-      <c r="D57" t="str">
-        <v>soda(苏打)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>I</v>
-      </c>
-      <c r="C58" t="str">
-        <v>我</v>
-      </c>
-      <c r="D58" t="str">
-        <v>I(我)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>skill</v>
-      </c>
-      <c r="C59" t="str">
-        <v>技能</v>
-      </c>
-      <c r="D59" t="str">
-        <v>skill(技能)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>course</v>
-      </c>
-      <c r="C60" t="str">
-        <v>课程</v>
-      </c>
-      <c r="D60" t="str">
-        <v>course(课程)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>splendid</v>
-      </c>
-      <c r="C61" t="str">
-        <v>极好的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>splendid(极好的)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>excessive</v>
-      </c>
-      <c r="C62" t="str">
-        <v>过多</v>
-      </c>
-      <c r="D62" t="str">
-        <v>excessive(过多)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>pill</v>
-      </c>
-      <c r="C63" t="str">
-        <v>药丸</v>
-      </c>
-      <c r="D63" t="str">
-        <v>pill(药丸)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>bed</v>
-      </c>
-      <c r="C64" t="str">
-        <v>床</v>
-      </c>
-      <c r="D64" t="str">
-        <v>bed(床)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>minimum</v>
-      </c>
-      <c r="C65" t="str">
-        <v>最小</v>
-      </c>
-      <c r="D65" t="str">
-        <v>minimum(最小)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>flour</v>
-      </c>
-      <c r="C66" t="str">
-        <v>面粉</v>
-      </c>
-      <c r="D66" t="str">
-        <v>flour(面粉)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>beer</v>
-      </c>
-      <c r="C67" t="str">
-        <v>啤酒</v>
-      </c>
-      <c r="D67" t="str">
-        <v>beer(啤酒)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>believe</v>
-      </c>
-      <c r="C68" t="str">
         <v>相信</v>
-      </c>
-      <c r="D68" t="str">
-        <v>believe(相信)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>splendid</v>
-      </c>
-      <c r="C69" t="str">
-        <v>极好的</v>
-      </c>
-      <c r="D69" t="str">
-        <v>splendid(极好的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
   </ignoredErrors>
 </worksheet>
 </file>